--- a/data/trans_bre/P29A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -12,31</t>
+          <t>-26,71; -12,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,55; -14,23</t>
+          <t>-29,16; -13,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,36; -15,88</t>
+          <t>-30,64; -15,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,93; -13,32</t>
+          <t>-25,63; -13,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -21,82</t>
+          <t>-43,86; -22,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,23; -23,13</t>
+          <t>-43,97; -22,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -25,45</t>
+          <t>-44,38; -24,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,89; -25,59</t>
+          <t>-43,26; -25,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -14,56</t>
+          <t>-28,71; -14,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,28; -12,7</t>
+          <t>-29,16; -13,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -5,81</t>
+          <t>-20,66; -5,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -5,56</t>
+          <t>-17,77; -5,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,2; -25,34</t>
+          <t>-45,78; -26,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,3; -23,32</t>
+          <t>-47,55; -23,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,42; -9,74</t>
+          <t>-31,65; -8,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,27; -12,67</t>
+          <t>-35,61; -12,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,24; -17,07</t>
+          <t>-34,35; -17,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-38,89; -24,35</t>
+          <t>-39,02; -25,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,41; -21,28</t>
+          <t>-39,13; -20,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 19,3</t>
+          <t>-28,09; 14,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,28; -29,28</t>
+          <t>-55,86; -29,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,74; -44,45</t>
+          <t>-65,65; -44,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,2; -35,2</t>
+          <t>-61,75; -35,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 147,35</t>
+          <t>-55,95; 92,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,66; -21,02</t>
+          <t>-29,48; -20,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,15; -22,2</t>
+          <t>-31,43; -22,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -17,11</t>
+          <t>-25,61; -16,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 19,05</t>
+          <t>-23,89; 24,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -41,94</t>
+          <t>-55,7; -41,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,14; -43,46</t>
+          <t>-57,6; -44,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,94; -31,76</t>
+          <t>-44,63; -30,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 40,32</t>
+          <t>-47,36; 52,58</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,97; -29,36</t>
+          <t>-42,17; -29,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -30,45</t>
+          <t>-41,56; -30,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,59; -20,28</t>
+          <t>-30,59; -20,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,65; -27,53</t>
+          <t>-39,8; -27,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,76; -53,76</t>
+          <t>-68,05; -53,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -56,02</t>
+          <t>-69,37; -57,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-59,21; -43,68</t>
+          <t>-58,83; -43,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,05; -61,33</t>
+          <t>-77,1; -61,63</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -23,17</t>
+          <t>-35,28; -23,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,04; -22,71</t>
+          <t>-35,64; -22,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,07; -23,27</t>
+          <t>-36,6; -23,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -12,08</t>
+          <t>-34,16; -11,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,47; -57,18</t>
+          <t>-71,02; -57,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,8; -50,83</t>
+          <t>-64,99; -50,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,18; -48,83</t>
+          <t>-63,29; -49,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,88; -41,9</t>
+          <t>-69,41; -41,44</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-32,72; -28,15</t>
+          <t>-32,63; -27,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -28,13</t>
+          <t>-32,82; -27,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,89; -24,15</t>
+          <t>-28,86; -24,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,3; -0,97</t>
+          <t>-25,34; -1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -52,34</t>
+          <t>-58,33; -52,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -51,04</t>
+          <t>-57,12; -51,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,53; -43,06</t>
+          <t>-49,62; -43,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -1,92</t>
+          <t>-51,77; -2,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P29A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-19,79</t>
+          <t>-19,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-35,24%</t>
+          <t>-35,09%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,71; -12,23</t>
+          <t>-27,02; -12,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -13,65</t>
+          <t>-29,43; -13,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -15,72</t>
+          <t>-30,36; -15,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -13,58</t>
+          <t>-24,91; -13,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,86; -22,55</t>
+          <t>-44,32; -22,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,97; -22,76</t>
+          <t>-44,31; -22,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,38; -24,87</t>
+          <t>-44,37; -24,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,26; -25,58</t>
+          <t>-42,92; -26,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,97</t>
+          <t>-11,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-25,42%</t>
+          <t>-25,71%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,71; -14,59</t>
+          <t>-29,28; -13,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -13,12</t>
+          <t>-29,11; -13,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,66; -5,13</t>
+          <t>-20,35; -6,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -5,45</t>
+          <t>-18,45; -5,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,78; -26,3</t>
+          <t>-46,69; -24,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -23,84</t>
+          <t>-46,87; -24,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -8,82</t>
+          <t>-30,85; -9,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,61; -12,9</t>
+          <t>-36,62; -13,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,3</t>
+          <t>-23,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-23,11%</t>
+          <t>-48,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -17,56</t>
+          <t>-34,34; -17,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,02; -25,15</t>
+          <t>-38,57; -23,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,13; -20,83</t>
+          <t>-38,72; -21,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 14,34</t>
+          <t>-29,94; -16,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,86; -29,82</t>
+          <t>-56,64; -30,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,65; -44,72</t>
+          <t>-65,22; -44,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,75; -35,62</t>
+          <t>-61,13; -35,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 92,54</t>
+          <t>-59,39; -35,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-21,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-14,17%</t>
+          <t>-44,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,48; -20,51</t>
+          <t>-29,77; -20,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; -22,39</t>
+          <t>-31,36; -22,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,61; -16,68</t>
+          <t>-25,37; -16,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 24,38</t>
+          <t>-25,57; -16,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,7; -41,77</t>
+          <t>-56,32; -42,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,6; -44,1</t>
+          <t>-57,31; -43,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,63; -30,63</t>
+          <t>-44,41; -30,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 52,58</t>
+          <t>-50,62; -36,51</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-33,38</t>
+          <t>-27,08</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-68,14%</t>
+          <t>-59,48%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -29,36</t>
+          <t>-42,02; -29,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-41,56; -30,78</t>
+          <t>-41,51; -31,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,59; -20,0</t>
+          <t>-30,31; -19,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,8; -27,7</t>
+          <t>-32,41; -22,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,05; -53,35</t>
+          <t>-67,88; -53,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,37; -57,09</t>
+          <t>-69,26; -57,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,83; -43,07</t>
+          <t>-59,27; -43,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-77,1; -61,63</t>
+          <t>-65,49; -51,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-23,37</t>
+          <t>-21,08</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-59,25%</t>
+          <t>-58,26%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -23,17</t>
+          <t>-34,81; -23,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -22,56</t>
+          <t>-35,62; -21,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -23,19</t>
+          <t>-37,34; -23,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -11,97</t>
+          <t>-31,24; -11,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,02; -57,95</t>
+          <t>-70,57; -57,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,99; -50,4</t>
+          <t>-64,85; -49,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,29; -49,84</t>
+          <t>-64,02; -49,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,41; -41,44</t>
+          <t>-69,68; -41,06</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-17,68</t>
+          <t>-23,66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-38,57%</t>
+          <t>-49,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-32,63; -27,97</t>
+          <t>-32,72; -28,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -27,9</t>
+          <t>-32,61; -27,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,86; -24,08</t>
+          <t>-28,81; -24,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,34; -1,31</t>
+          <t>-25,9; -21,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -52,22</t>
+          <t>-58,2; -52,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -51,01</t>
+          <t>-57,08; -50,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,62; -43,01</t>
+          <t>-49,49; -42,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,77; -2,01</t>
+          <t>-52,59; -46,11</t>
         </is>
       </c>
     </row>
